--- a/update-record-page/catalog_summary.xlsx
+++ b/update-record-page/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA261"/>
+  <dimension ref="A1:AA260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,22 +514,22 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>sum</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ERROR</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -639,16 +639,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>2</v>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -748,14 +748,14 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
         <v>2</v>
       </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>3</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -968,16 +968,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
@@ -1087,14 +1087,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>7</v>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="n">
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
         <v>7</v>
       </c>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
@@ -1204,16 +1204,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>6</v>
       </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>7</v>
       </c>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
@@ -1319,16 +1319,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>3</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>6</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>9</v>
       </c>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1424,16 +1424,16 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>4</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>5</v>
       </c>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1530,16 +1530,16 @@
         </is>
       </c>
       <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
         <v>2</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
+          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegetated Islands Polygons - 100 Islands Research</t>
+          <t>Northwest Calvert Substrate Mapping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1608,47 +1608,61 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[{'max': '600.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10.21966/35tn-w772</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
       <c r="W11" t="n">
-        <v>6</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1656,12 +1670,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
+          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1671,7 +1685,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Northwest Calvert Substrate Mapping</t>
+          <t>Vegetated Islands Polygons - 100 Islands Research</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1689,7 +1703,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1713,16 +1727,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[{'max': '600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1730,11 +1744,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>10.21966/35tn-w772</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>2021-09-23</t>
@@ -1742,32 +1752,22 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,16 +1860,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
         <v>2</v>
       </c>
       <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
         <v>4</v>
       </c>
-      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1966,16 +1966,16 @@
         </is>
       </c>
       <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
         <v>6</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>3</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>10</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -2076,16 +2076,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
         <v>2</v>
       </c>
       <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
         <v>4</v>
       </c>
-      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
@@ -2195,16 +2195,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>2</v>
       </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
         <v>3</v>
       </c>
-      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
@@ -2314,16 +2314,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>3</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>2</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>5</v>
       </c>
-      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
         <v>1</v>
       </c>
@@ -2433,16 +2433,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>8</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>5</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>13</v>
       </c>
-      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
@@ -2549,14 +2549,14 @@
         </is>
       </c>
       <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="n">
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
         <v>3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2663,16 +2663,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
         <v>2</v>
       </c>
-      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -2772,16 +2772,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
         <v>2</v>
       </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
         <v>3</v>
       </c>
-      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
@@ -2888,16 +2888,16 @@
         </is>
       </c>
       <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
         <v>4</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>5</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>10</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>2</v>
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
         <v>6</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>3</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>10</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>2</v>
@@ -3130,16 +3130,16 @@
         </is>
       </c>
       <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
         <v>2</v>
       </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
         <v>4</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3246,16 +3246,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>4</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>5</v>
       </c>
-      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -3355,16 +3355,16 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>2</v>
       </c>
-      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
         <v>1</v>
       </c>
@@ -3474,16 +3474,16 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
         <v>5</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>4</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>9</v>
       </c>
-      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
@@ -3593,16 +3593,16 @@
           <t>2024-08-02</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
         <v>4</v>
       </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
         <v>5</v>
       </c>
-      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
@@ -3712,16 +3712,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
         <v>4</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>5</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>9</v>
       </c>
-      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
@@ -3831,16 +3831,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>2</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>3</v>
       </c>
-      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
@@ -3950,16 +3950,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
         <v>2</v>
       </c>
       <c r="W31" t="n">
+        <v>2</v>
+      </c>
+      <c r="X31" t="n">
         <v>4</v>
       </c>
-      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
@@ -4069,16 +4069,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U32" t="n">
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
         <v>2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
       <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
         <v>3</v>
       </c>
-      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
@@ -4188,16 +4188,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>3</v>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
         <v>3</v>
       </c>
       <c r="W33" t="n">
+        <v>3</v>
+      </c>
+      <c r="X33" t="n">
         <v>6</v>
       </c>
-      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
@@ -4303,16 +4303,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U34" t="n">
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
         <v>4</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>5</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>9</v>
       </c>
-      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -4408,16 +4408,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
         <v>3</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>6</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>9</v>
       </c>
-      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -4518,16 +4518,16 @@
         </is>
       </c>
       <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
         <v>2</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>5</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>8</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -4638,16 +4638,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>2</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>3</v>
       </c>
-      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
         <v>0</v>
       </c>
@@ -4753,16 +4753,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
         <v>2</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>6</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>8</v>
       </c>
-      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -4862,16 +4862,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U39" t="n">
-        <v>2</v>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
         <v>2</v>
       </c>
       <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="n">
         <v>4</v>
       </c>
-      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
@@ -4977,16 +4977,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
         <v>2</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>3</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>5</v>
       </c>
-      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -5082,16 +5082,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U41" t="n">
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
         <v>3</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>6</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>9</v>
       </c>
-      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
@@ -5191,16 +5191,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
         <v>4</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>5</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>9</v>
       </c>
-      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
         <v>1</v>
       </c>
@@ -5306,16 +5306,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>3</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>4</v>
       </c>
-      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -5415,16 +5415,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
         <v>2</v>
       </c>
-      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
         <v>0</v>
       </c>
@@ -5530,16 +5530,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
         <v>2</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>6</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>8</v>
       </c>
-      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
@@ -5635,16 +5635,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>4</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>5</v>
       </c>
-      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
@@ -5744,16 +5744,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>2</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>3</v>
       </c>
-      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
@@ -5859,16 +5859,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
         <v>5</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>9</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>14</v>
       </c>
-      <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
@@ -5968,16 +5968,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U49" t="n">
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
         <v>2</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>5</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>7</v>
       </c>
-      <c r="X49" t="inlineStr"/>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
@@ -6087,14 +6087,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U50" t="n">
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
         <v>2</v>
       </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="n">
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="n">
         <v>2</v>
       </c>
-      <c r="X50" t="inlineStr"/>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
@@ -6204,16 +6204,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U51" t="n">
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
         <v>2</v>
       </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
       <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
         <v>3</v>
       </c>
-      <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
         <v>0</v>
       </c>
@@ -6323,16 +6323,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U52" t="n">
-        <v>2</v>
-      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
         <v>2</v>
       </c>
       <c r="W52" t="n">
+        <v>2</v>
+      </c>
+      <c r="X52" t="n">
         <v>4</v>
       </c>
-      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="n">
         <v>0</v>
       </c>
@@ -6442,16 +6442,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U53" t="n">
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="n">
         <v>2</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>5</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>7</v>
       </c>
-      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="n">
         <v>0</v>
       </c>
@@ -6561,14 +6561,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
       <c r="Y54" t="n">
         <v>0</v>
       </c>
@@ -6678,14 +6678,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="n">
         <v>3</v>
       </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="n">
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="n">
         <v>3</v>
       </c>
-      <c r="X55" t="inlineStr"/>
       <c r="Y55" t="n">
         <v>0</v>
       </c>
@@ -6795,16 +6795,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U56" t="n">
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="n">
         <v>2</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>4</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>6</v>
       </c>
-      <c r="X56" t="inlineStr"/>
       <c r="Y56" t="n">
         <v>0</v>
       </c>
@@ -6911,16 +6911,16 @@
         </is>
       </c>
       <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
         <v>4</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>5</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>10</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1</v>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
@@ -7021,16 +7021,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="n">
         <v>2</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>7</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>9</v>
       </c>
-      <c r="X58" t="inlineStr"/>
       <c r="Y58" t="n">
         <v>0</v>
       </c>
@@ -7140,16 +7140,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U59" t="n">
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="n">
         <v>6</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>4</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>10</v>
       </c>
-      <c r="X59" t="inlineStr"/>
       <c r="Y59" t="n">
         <v>0</v>
       </c>
@@ -7259,16 +7259,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U60" t="n">
-        <v>1</v>
-      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" t="n">
         <v>2</v>
       </c>
-      <c r="X60" t="inlineStr"/>
       <c r="Y60" t="n">
         <v>3</v>
       </c>
@@ -7378,14 +7378,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="n">
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
         <v>2</v>
       </c>
-      <c r="X61" t="inlineStr"/>
       <c r="Y61" t="n">
         <v>0</v>
       </c>
@@ -7495,14 +7495,14 @@
           <t>2024-08-02</t>
         </is>
       </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
       <c r="Y62" t="n">
         <v>0</v>
       </c>
@@ -7612,16 +7612,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
         <v>2</v>
       </c>
-      <c r="X63" t="inlineStr"/>
       <c r="Y63" t="n">
         <v>0</v>
       </c>
@@ -7728,16 +7728,16 @@
         </is>
       </c>
       <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
         <v>2</v>
       </c>
-      <c r="V64" t="n">
+      <c r="W64" t="n">
         <v>4</v>
       </c>
-      <c r="W64" t="n">
+      <c r="X64" t="n">
         <v>7</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="U65" t="n">
-        <v>1</v>
-      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" t="n">
         <v>2</v>
       </c>
-      <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
@@ -7949,16 +7949,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="n">
         <v>3</v>
       </c>
-      <c r="V66" t="n">
+      <c r="W66" t="n">
         <v>4</v>
       </c>
-      <c r="W66" t="n">
+      <c r="X66" t="n">
         <v>7</v>
       </c>
-      <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
@@ -8058,16 +8058,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="n">
         <v>2</v>
       </c>
-      <c r="V67" t="n">
+      <c r="W67" t="n">
         <v>5</v>
       </c>
-      <c r="W67" t="n">
+      <c r="X67" t="n">
         <v>7</v>
       </c>
-      <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
         <v>0</v>
       </c>
@@ -8177,14 +8177,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
       <c r="Y68" t="n">
         <v>1</v>
       </c>
@@ -8294,16 +8294,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="n">
         <v>5</v>
       </c>
-      <c r="V69" t="n">
+      <c r="W69" t="n">
         <v>3</v>
       </c>
-      <c r="W69" t="n">
+      <c r="X69" t="n">
         <v>8</v>
       </c>
-      <c r="X69" t="inlineStr"/>
       <c r="Y69" t="n">
         <v>0</v>
       </c>
@@ -8413,16 +8413,16 @@
           <t>2024-11-25</t>
         </is>
       </c>
-      <c r="U70" t="n">
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="n">
         <v>4</v>
       </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
       <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="n">
         <v>5</v>
       </c>
-      <c r="X70" t="inlineStr"/>
       <c r="Y70" t="n">
         <v>0</v>
       </c>
@@ -8532,16 +8532,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U71" t="n">
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="n">
         <v>2</v>
       </c>
-      <c r="V71" t="n">
+      <c r="W71" t="n">
         <v>4</v>
       </c>
-      <c r="W71" t="n">
+      <c r="X71" t="n">
         <v>6</v>
       </c>
-      <c r="X71" t="inlineStr"/>
       <c r="Y71" t="n">
         <v>0</v>
       </c>
@@ -8651,14 +8651,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="n">
         <v>2</v>
       </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="n">
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="n">
         <v>2</v>
       </c>
-      <c r="X72" t="inlineStr"/>
       <c r="Y72" t="n">
         <v>0</v>
       </c>
@@ -8768,14 +8768,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U73" t="n">
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="n">
         <v>2</v>
       </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="n">
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="n">
         <v>2</v>
       </c>
-      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="n">
         <v>0</v>
       </c>
@@ -8886,14 +8886,14 @@
         </is>
       </c>
       <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
         <v>2</v>
       </c>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="n">
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="n">
         <v>3</v>
-      </c>
-      <c r="X74" t="n">
-        <v>1</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -9004,16 +9004,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U75" t="n">
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="n">
         <v>6</v>
       </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>2</v>
       </c>
-      <c r="W75" t="n">
+      <c r="X75" t="n">
         <v>8</v>
       </c>
-      <c r="X75" t="inlineStr"/>
       <c r="Y75" t="n">
         <v>0</v>
       </c>
@@ -9123,16 +9123,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U76" t="n">
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="n">
         <v>2</v>
       </c>
-      <c r="V76" t="n">
+      <c r="W76" t="n">
         <v>3</v>
       </c>
-      <c r="W76" t="n">
+      <c r="X76" t="n">
         <v>5</v>
       </c>
-      <c r="X76" t="inlineStr"/>
       <c r="Y76" t="n">
         <v>0</v>
       </c>
@@ -9238,13 +9238,13 @@
         <v>1</v>
       </c>
       <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="W77" t="n">
         <v>8</v>
       </c>
-      <c r="W77" t="n">
+      <c r="X77" t="n">
         <v>10</v>
-      </c>
-      <c r="X77" t="n">
-        <v>1</v>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
@@ -9341,16 +9341,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
         <v>4</v>
       </c>
-      <c r="W78" t="n">
+      <c r="X78" t="n">
         <v>5</v>
       </c>
-      <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
@@ -9446,16 +9446,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U79" t="n">
-        <v>1</v>
-      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" t="n">
         <v>6</v>
       </c>
-      <c r="W79" t="n">
+      <c r="X79" t="n">
         <v>7</v>
       </c>
-      <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -9551,13 +9551,13 @@
         <v>1</v>
       </c>
       <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
         <v>8</v>
       </c>
-      <c r="W80" t="n">
+      <c r="X80" t="n">
         <v>10</v>
-      </c>
-      <c r="X80" t="n">
-        <v>1</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
@@ -9654,13 +9654,13 @@
         <v>1</v>
       </c>
       <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" t="n">
         <v>9</v>
       </c>
-      <c r="W81" t="n">
+      <c r="X81" t="n">
         <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>1</v>
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
@@ -9757,13 +9757,13 @@
         <v>1</v>
       </c>
       <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" t="n">
         <v>9</v>
       </c>
-      <c r="W82" t="n">
+      <c r="X82" t="n">
         <v>11</v>
-      </c>
-      <c r="X82" t="n">
-        <v>1</v>
       </c>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
@@ -9864,16 +9864,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U83" t="n">
-        <v>1</v>
-      </c>
+      <c r="U83" t="inlineStr"/>
       <c r="V83" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" t="n">
         <v>3</v>
       </c>
-      <c r="W83" t="n">
+      <c r="X83" t="n">
         <v>4</v>
       </c>
-      <c r="X83" t="inlineStr"/>
       <c r="Y83" t="n">
         <v>0</v>
       </c>
@@ -9987,13 +9987,13 @@
         <v>1</v>
       </c>
       <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
         <v>3</v>
       </c>
-      <c r="W84" t="n">
+      <c r="X84" t="n">
         <v>5</v>
-      </c>
-      <c r="X84" t="n">
-        <v>1</v>
       </c>
       <c r="Y84" t="n">
         <v>0</v>
@@ -10100,13 +10100,13 @@
         <v>1</v>
       </c>
       <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
         <v>4</v>
       </c>
-      <c r="W85" t="n">
+      <c r="X85" t="n">
         <v>6</v>
-      </c>
-      <c r="X85" t="n">
-        <v>1</v>
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
@@ -10203,13 +10203,13 @@
         <v>1</v>
       </c>
       <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
         <v>8</v>
       </c>
-      <c r="W86" t="n">
+      <c r="X86" t="n">
         <v>10</v>
-      </c>
-      <c r="X86" t="n">
-        <v>1</v>
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
@@ -10306,16 +10306,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U87" t="n">
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="n">
         <v>2</v>
       </c>
-      <c r="V87" t="n">
+      <c r="W87" t="n">
         <v>5</v>
       </c>
-      <c r="W87" t="n">
+      <c r="X87" t="n">
         <v>7</v>
       </c>
-      <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
@@ -10416,14 +10416,14 @@
         </is>
       </c>
       <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="n">
         <v>4</v>
       </c>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="n">
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="n">
         <v>5</v>
-      </c>
-      <c r="X88" t="n">
-        <v>1</v>
       </c>
       <c r="Y88" t="n">
         <v>0</v>
@@ -10534,16 +10534,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U89" t="n">
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="n">
         <v>2</v>
       </c>
-      <c r="V89" t="n">
+      <c r="W89" t="n">
         <v>3</v>
       </c>
-      <c r="W89" t="n">
+      <c r="X89" t="n">
         <v>5</v>
       </c>
-      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="n">
         <v>0</v>
       </c>
@@ -10654,16 +10654,16 @@
         </is>
       </c>
       <c r="U90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>2</v>
       </c>
       <c r="W90" t="n">
+        <v>2</v>
+      </c>
+      <c r="X90" t="n">
         <v>5</v>
-      </c>
-      <c r="X90" t="n">
-        <v>1</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -10774,16 +10774,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" t="n">
         <v>2</v>
       </c>
-      <c r="W91" t="n">
+      <c r="X91" t="n">
         <v>3</v>
       </c>
-      <c r="X91" t="inlineStr"/>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
@@ -10893,16 +10893,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U92" t="n">
-        <v>2</v>
-      </c>
+      <c r="U92" t="inlineStr"/>
       <c r="V92" t="n">
         <v>2</v>
       </c>
       <c r="W92" t="n">
+        <v>2</v>
+      </c>
+      <c r="X92" t="n">
         <v>4</v>
       </c>
-      <c r="X92" t="inlineStr"/>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
@@ -11012,16 +11012,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U93" t="n">
-        <v>1</v>
-      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" t="n">
         <v>2</v>
       </c>
-      <c r="W93" t="n">
+      <c r="X93" t="n">
         <v>3</v>
       </c>
-      <c r="X93" t="inlineStr"/>
       <c r="Y93" t="n">
         <v>0</v>
       </c>
@@ -11127,16 +11127,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U94" t="n">
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="n">
         <v>5</v>
       </c>
-      <c r="V94" t="n">
+      <c r="W94" t="n">
         <v>3</v>
       </c>
-      <c r="W94" t="n">
+      <c r="X94" t="n">
         <v>8</v>
       </c>
-      <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
@@ -11229,16 +11229,16 @@
         </is>
       </c>
       <c r="U95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
         <v>3</v>
       </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
       <c r="W95" t="n">
+        <v>1</v>
+      </c>
+      <c r="X95" t="n">
         <v>5</v>
-      </c>
-      <c r="X95" t="n">
-        <v>1</v>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -11335,16 +11335,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U96" t="n">
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="n">
         <v>2</v>
       </c>
-      <c r="V96" t="n">
+      <c r="W96" t="n">
         <v>6</v>
       </c>
-      <c r="W96" t="n">
+      <c r="X96" t="n">
         <v>8</v>
       </c>
-      <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr"/>
@@ -11440,16 +11440,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U97" t="n">
-        <v>1</v>
-      </c>
+      <c r="U97" t="inlineStr"/>
       <c r="V97" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" t="n">
         <v>7</v>
       </c>
-      <c r="W97" t="n">
+      <c r="X97" t="n">
         <v>8</v>
       </c>
-      <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
@@ -11546,16 +11546,16 @@
         </is>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" t="n">
         <v>7</v>
       </c>
-      <c r="W98" t="n">
+      <c r="X98" t="n">
         <v>10</v>
-      </c>
-      <c r="X98" t="n">
-        <v>2</v>
       </c>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
@@ -11656,16 +11656,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U99" t="n">
-        <v>1</v>
-      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="n">
+        <v>1</v>
+      </c>
+      <c r="W99" t="n">
         <v>3</v>
       </c>
-      <c r="W99" t="n">
+      <c r="X99" t="n">
         <v>4</v>
       </c>
-      <c r="X99" t="inlineStr"/>
       <c r="Y99" t="n">
         <v>0</v>
       </c>
@@ -11771,13 +11771,13 @@
         <v>1</v>
       </c>
       <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="W100" t="n">
         <v>5</v>
       </c>
-      <c r="W100" t="n">
+      <c r="X100" t="n">
         <v>7</v>
-      </c>
-      <c r="X100" t="n">
-        <v>1</v>
       </c>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
@@ -11878,16 +11878,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
+      <c r="U101" t="inlineStr"/>
       <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
         <v>2</v>
       </c>
-      <c r="W101" t="n">
+      <c r="X101" t="n">
         <v>3</v>
       </c>
-      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="n">
         <v>0</v>
       </c>
@@ -11997,14 +11997,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="n">
-        <v>1</v>
-      </c>
-      <c r="X102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="n">
+        <v>1</v>
+      </c>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
       <c r="Y102" t="n">
         <v>0</v>
       </c>
@@ -12114,16 +12114,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U103" t="n">
-        <v>2</v>
-      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="n">
         <v>2</v>
       </c>
       <c r="W103" t="n">
+        <v>2</v>
+      </c>
+      <c r="X103" t="n">
         <v>4</v>
       </c>
-      <c r="X103" t="inlineStr"/>
       <c r="Y103" t="n">
         <v>0</v>
       </c>
@@ -12229,16 +12229,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U104" t="n">
-        <v>1</v>
-      </c>
+      <c r="U104" t="inlineStr"/>
       <c r="V104" t="n">
+        <v>1</v>
+      </c>
+      <c r="W104" t="n">
         <v>6</v>
       </c>
-      <c r="W104" t="n">
+      <c r="X104" t="n">
         <v>7</v>
       </c>
-      <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr"/>
@@ -12249,12 +12249,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12280,14 +12280,10 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -12306,16 +12302,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -12331,19 +12327,21 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="U105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
         <v>8</v>
       </c>
-      <c r="X105" t="inlineStr"/>
+      <c r="X105" t="n">
+        <v>10</v>
+      </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
@@ -12354,12 +12352,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -12369,7 +12367,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -12385,10 +12383,14 @@
       <c r="H106" t="b">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12407,16 +12409,16 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -12432,20 +12434,18 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
       <c r="V106" t="n">
+        <v>2</v>
+      </c>
+      <c r="W106" t="n">
+        <v>6</v>
+      </c>
+      <c r="X106" t="n">
         <v>8</v>
-      </c>
-      <c r="W106" t="n">
-        <v>10</v>
-      </c>
-      <c r="X106" t="n">
-        <v>1</v>
       </c>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
@@ -12542,16 +12542,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U107" t="n">
-        <v>1</v>
-      </c>
+      <c r="U107" t="inlineStr"/>
       <c r="V107" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" t="n">
         <v>5</v>
       </c>
-      <c r="W107" t="n">
+      <c r="X107" t="n">
         <v>6</v>
       </c>
-      <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr"/>
@@ -12651,16 +12651,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U108" t="n">
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="n">
         <v>2</v>
       </c>
-      <c r="V108" t="n">
+      <c r="W108" t="n">
         <v>3</v>
       </c>
-      <c r="W108" t="n">
+      <c r="X108" t="n">
         <v>5</v>
       </c>
-      <c r="X108" t="inlineStr"/>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
@@ -12770,16 +12770,16 @@
           <t>2025-01-03</t>
         </is>
       </c>
-      <c r="U109" t="n">
-        <v>1</v>
-      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="n">
+        <v>1</v>
+      </c>
+      <c r="W109" t="n">
         <v>3</v>
       </c>
-      <c r="W109" t="n">
+      <c r="X109" t="n">
         <v>4</v>
       </c>
-      <c r="X109" t="inlineStr"/>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
@@ -12889,16 +12889,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U110" t="n">
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="n">
         <v>2</v>
       </c>
-      <c r="V110" t="n">
+      <c r="W110" t="n">
         <v>3</v>
       </c>
-      <c r="W110" t="n">
+      <c r="X110" t="n">
         <v>5</v>
       </c>
-      <c r="X110" t="inlineStr"/>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
@@ -13004,16 +13004,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U111" t="n">
-        <v>1</v>
-      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="n">
+        <v>1</v>
+      </c>
+      <c r="W111" t="n">
         <v>5</v>
       </c>
-      <c r="W111" t="n">
+      <c r="X111" t="n">
         <v>6</v>
       </c>
-      <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr"/>
@@ -13109,16 +13109,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U112" t="n">
-        <v>1</v>
-      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="n">
+        <v>1</v>
+      </c>
+      <c r="W112" t="n">
         <v>3</v>
       </c>
-      <c r="W112" t="n">
+      <c r="X112" t="n">
         <v>4</v>
       </c>
-      <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
@@ -13214,16 +13214,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U113" t="n">
-        <v>1</v>
-      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="n">
+        <v>1</v>
+      </c>
+      <c r="W113" t="n">
         <v>8</v>
       </c>
-      <c r="W113" t="n">
+      <c r="X113" t="n">
         <v>9</v>
       </c>
-      <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr"/>
@@ -13319,16 +13319,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U114" t="n">
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="n">
         <v>2</v>
       </c>
-      <c r="V114" t="n">
+      <c r="W114" t="n">
         <v>7</v>
       </c>
-      <c r="W114" t="n">
+      <c r="X114" t="n">
         <v>9</v>
       </c>
-      <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="inlineStr"/>
@@ -13424,13 +13424,13 @@
         <v>1</v>
       </c>
       <c r="V115" t="n">
+        <v>1</v>
+      </c>
+      <c r="W115" t="n">
         <v>8</v>
       </c>
-      <c r="W115" t="n">
+      <c r="X115" t="n">
         <v>10</v>
-      </c>
-      <c r="X115" t="n">
-        <v>1</v>
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
@@ -13527,13 +13527,13 @@
         <v>1</v>
       </c>
       <c r="V116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" t="n">
         <v>10</v>
       </c>
-      <c r="W116" t="n">
+      <c r="X116" t="n">
         <v>12</v>
-      </c>
-      <c r="X116" t="n">
-        <v>1</v>
       </c>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
@@ -13630,16 +13630,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U117" t="n">
-        <v>1</v>
-      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="n">
+        <v>1</v>
+      </c>
+      <c r="W117" t="n">
         <v>6</v>
       </c>
-      <c r="W117" t="n">
+      <c r="X117" t="n">
         <v>7</v>
       </c>
-      <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
@@ -13739,16 +13739,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U118" t="n">
-        <v>1</v>
-      </c>
+      <c r="U118" t="inlineStr"/>
       <c r="V118" t="n">
+        <v>1</v>
+      </c>
+      <c r="W118" t="n">
         <v>3</v>
       </c>
-      <c r="W118" t="n">
+      <c r="X118" t="n">
         <v>4</v>
       </c>
-      <c r="X118" t="inlineStr"/>
       <c r="Y118" t="n">
         <v>0</v>
       </c>
@@ -13859,16 +13859,16 @@
         </is>
       </c>
       <c r="U119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
         <v>3</v>
       </c>
-      <c r="V119" t="n">
+      <c r="W119" t="n">
         <v>6</v>
       </c>
-      <c r="W119" t="n">
+      <c r="X119" t="n">
         <v>10</v>
-      </c>
-      <c r="X119" t="n">
-        <v>1</v>
       </c>
       <c r="Y119" t="n">
         <v>0</v>
@@ -13976,16 +13976,16 @@
         </is>
       </c>
       <c r="U120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
         <v>3</v>
       </c>
-      <c r="V120" t="n">
-        <v>1</v>
-      </c>
       <c r="W120" t="n">
+        <v>1</v>
+      </c>
+      <c r="X120" t="n">
         <v>5</v>
-      </c>
-      <c r="X120" t="n">
-        <v>1</v>
       </c>
       <c r="Y120" t="n">
         <v>0</v>
@@ -14096,14 +14096,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="n">
-        <v>1</v>
-      </c>
-      <c r="X121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
       <c r="Y121" t="n">
         <v>1</v>
       </c>
@@ -14213,14 +14213,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="U122" t="n">
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="n">
         <v>3</v>
       </c>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="n">
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="n">
         <v>3</v>
       </c>
-      <c r="X122" t="inlineStr"/>
       <c r="Y122" t="n">
         <v>1</v>
       </c>
@@ -14330,16 +14330,16 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="U123" t="n">
-        <v>5</v>
-      </c>
+      <c r="U123" t="inlineStr"/>
       <c r="V123" t="n">
         <v>5</v>
       </c>
       <c r="W123" t="n">
+        <v>5</v>
+      </c>
+      <c r="X123" t="n">
         <v>10</v>
       </c>
-      <c r="X123" t="inlineStr"/>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
@@ -14445,16 +14445,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U124" t="n">
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="n">
         <v>2</v>
       </c>
-      <c r="V124" t="n">
+      <c r="W124" t="n">
         <v>4</v>
       </c>
-      <c r="W124" t="n">
+      <c r="X124" t="n">
         <v>6</v>
       </c>
-      <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr"/>
@@ -14554,16 +14554,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U125" t="n">
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="n">
         <v>3</v>
       </c>
-      <c r="V125" t="n">
+      <c r="W125" t="n">
         <v>2</v>
       </c>
-      <c r="W125" t="n">
+      <c r="X125" t="n">
         <v>5</v>
       </c>
-      <c r="X125" t="inlineStr"/>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
@@ -14674,14 +14674,14 @@
         </is>
       </c>
       <c r="U126" t="n">
+        <v>2</v>
+      </c>
+      <c r="V126" t="n">
         <v>5</v>
       </c>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="n">
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="n">
         <v>7</v>
-      </c>
-      <c r="X126" t="n">
-        <v>2</v>
       </c>
       <c r="Y126" t="n">
         <v>1</v>
@@ -14792,16 +14792,16 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="U127" t="n">
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="n">
         <v>3</v>
       </c>
-      <c r="V127" t="n">
+      <c r="W127" t="n">
         <v>5</v>
       </c>
-      <c r="W127" t="n">
+      <c r="X127" t="n">
         <v>8</v>
       </c>
-      <c r="X127" t="inlineStr"/>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
@@ -14822,12 +14822,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14879,16 +14879,16 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -14911,27 +14911,27 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U128" t="n">
-        <v>5</v>
-      </c>
+      <c r="U128" t="inlineStr"/>
       <c r="V128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W128" t="n">
-        <v>7</v>
-      </c>
-      <c r="X128" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="X128" t="n">
+        <v>8</v>
+      </c>
       <c r="Y128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
         </is>
       </c>
     </row>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14998,59 +14998,59 @@
         </is>
       </c>
       <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="n">
+        <v>5</v>
+      </c>
+      <c r="W129" t="n">
         <v>2</v>
       </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>10.21966/1.715755</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U129" t="n">
-        <v>4</v>
-      </c>
-      <c r="V129" t="n">
-        <v>4</v>
-      </c>
-      <c r="W129" t="n">
-        <v>8</v>
-      </c>
-      <c r="X129" t="inlineStr"/>
+      <c r="X129" t="n">
+        <v>7</v>
+      </c>
       <c r="Y129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -15149,14 +15149,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U130" t="n">
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="n">
         <v>2</v>
       </c>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="n">
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="n">
         <v>2</v>
       </c>
-      <c r="X130" t="inlineStr"/>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
@@ -15262,16 +15262,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U131" t="n">
-        <v>1</v>
-      </c>
+      <c r="U131" t="inlineStr"/>
       <c r="V131" t="n">
+        <v>1</v>
+      </c>
+      <c r="W131" t="n">
         <v>5</v>
       </c>
-      <c r="W131" t="n">
+      <c r="X131" t="n">
         <v>6</v>
       </c>
-      <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
@@ -15371,16 +15371,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U132" t="n">
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="n">
         <v>5</v>
       </c>
-      <c r="V132" t="n">
+      <c r="W132" t="n">
         <v>2</v>
       </c>
-      <c r="W132" t="n">
+      <c r="X132" t="n">
         <v>7</v>
       </c>
-      <c r="X132" t="inlineStr"/>
       <c r="Y132" t="n">
         <v>1</v>
       </c>
@@ -15490,14 +15490,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U133" t="n">
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="n">
         <v>2</v>
       </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="n">
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="n">
         <v>2</v>
       </c>
-      <c r="X133" t="inlineStr"/>
       <c r="Y133" t="n">
         <v>1</v>
       </c>
@@ -15604,16 +15604,16 @@
         </is>
       </c>
       <c r="U134" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" t="n">
         <v>11</v>
       </c>
-      <c r="V134" t="n">
+      <c r="W134" t="n">
         <v>5</v>
       </c>
-      <c r="W134" t="n">
+      <c r="X134" t="n">
         <v>17</v>
-      </c>
-      <c r="X134" t="n">
-        <v>1</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
@@ -15725,16 +15725,16 @@
         </is>
       </c>
       <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
         <v>11</v>
       </c>
-      <c r="V135" t="n">
-        <v>1</v>
-      </c>
       <c r="W135" t="n">
+        <v>1</v>
+      </c>
+      <c r="X135" t="n">
         <v>13</v>
-      </c>
-      <c r="X135" t="n">
-        <v>1</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
@@ -15842,16 +15842,16 @@
         </is>
       </c>
       <c r="U136" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V136" t="n">
         <v>5</v>
       </c>
       <c r="W136" t="n">
+        <v>5</v>
+      </c>
+      <c r="X136" t="n">
         <v>11</v>
-      </c>
-      <c r="X136" t="n">
-        <v>1</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
@@ -15962,14 +15962,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U137" t="n">
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="n">
         <v>2</v>
       </c>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="n">
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="n">
         <v>2</v>
       </c>
-      <c r="X137" t="inlineStr"/>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
@@ -16079,16 +16079,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U138" t="n">
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="n">
         <v>2</v>
       </c>
-      <c r="V138" t="n">
+      <c r="W138" t="n">
         <v>3</v>
       </c>
-      <c r="W138" t="n">
+      <c r="X138" t="n">
         <v>5</v>
       </c>
-      <c r="X138" t="inlineStr"/>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
@@ -16109,12 +16109,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16162,20 +16162,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -16183,7 +16183,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16191,24 +16195,34 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="U139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W139" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y139" t="inlineStr"/>
-      <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16216,12 +16230,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -16231,7 +16245,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -16249,7 +16263,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16269,20 +16283,20 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -16290,11 +16304,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16302,34 +16312,24 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="U140" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W140" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16422,16 +16422,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U141" t="n">
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="n">
         <v>2</v>
       </c>
-      <c r="V141" t="n">
+      <c r="W141" t="n">
         <v>8</v>
       </c>
-      <c r="W141" t="n">
+      <c r="X141" t="n">
         <v>10</v>
       </c>
-      <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr"/>
@@ -16531,16 +16531,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U142" t="n">
-        <v>1</v>
-      </c>
+      <c r="U142" t="inlineStr"/>
       <c r="V142" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" t="n">
         <v>2</v>
       </c>
-      <c r="W142" t="n">
+      <c r="X142" t="n">
         <v>3</v>
       </c>
-      <c r="X142" t="inlineStr"/>
       <c r="Y142" t="n">
         <v>1</v>
       </c>
@@ -16650,16 +16650,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U143" t="n">
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="n">
         <v>2</v>
       </c>
-      <c r="V143" t="n">
+      <c r="W143" t="n">
         <v>6</v>
       </c>
-      <c r="W143" t="n">
+      <c r="X143" t="n">
         <v>8</v>
       </c>
-      <c r="X143" t="inlineStr"/>
       <c r="Y143" t="n">
         <v>1</v>
       </c>
@@ -16769,16 +16769,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U144" t="n">
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="n">
         <v>2</v>
       </c>
-      <c r="V144" t="n">
+      <c r="W144" t="n">
         <v>4</v>
       </c>
-      <c r="W144" t="n">
+      <c r="X144" t="n">
         <v>6</v>
       </c>
-      <c r="X144" t="inlineStr"/>
       <c r="Y144" t="n">
         <v>1</v>
       </c>
@@ -16888,16 +16888,16 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="U145" t="n">
-        <v>1</v>
-      </c>
+      <c r="U145" t="inlineStr"/>
       <c r="V145" t="n">
+        <v>1</v>
+      </c>
+      <c r="W145" t="n">
         <v>2</v>
       </c>
-      <c r="W145" t="n">
+      <c r="X145" t="n">
         <v>3</v>
       </c>
-      <c r="X145" t="inlineStr"/>
       <c r="Y145" t="n">
         <v>2</v>
       </c>
@@ -17008,16 +17008,16 @@
         </is>
       </c>
       <c r="U146" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" t="n">
         <v>3</v>
       </c>
-      <c r="V146" t="n">
+      <c r="W146" t="n">
         <v>2</v>
       </c>
-      <c r="W146" t="n">
+      <c r="X146" t="n">
         <v>6</v>
-      </c>
-      <c r="X146" t="n">
-        <v>1</v>
       </c>
       <c r="Y146" t="n">
         <v>0</v>
@@ -17128,16 +17128,16 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="U147" t="n">
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="n">
         <v>4</v>
       </c>
-      <c r="V147" t="n">
+      <c r="W147" t="n">
         <v>2</v>
       </c>
-      <c r="W147" t="n">
+      <c r="X147" t="n">
         <v>6</v>
       </c>
-      <c r="X147" t="inlineStr"/>
       <c r="Y147" t="n">
         <v>1</v>
       </c>
@@ -17248,13 +17248,13 @@
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
-      <c r="V148" t="n">
-        <v>1</v>
-      </c>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="n">
         <v>1</v>
       </c>
-      <c r="X148" t="inlineStr"/>
+      <c r="X148" t="n">
+        <v>1</v>
+      </c>
       <c r="Y148" t="n">
         <v>0</v>
       </c>
@@ -17364,16 +17364,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U149" t="n">
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="n">
         <v>2</v>
       </c>
-      <c r="V149" t="n">
+      <c r="W149" t="n">
         <v>12</v>
       </c>
-      <c r="W149" t="n">
+      <c r="X149" t="n">
         <v>14</v>
       </c>
-      <c r="X149" t="inlineStr"/>
       <c r="Y149" t="n">
         <v>1</v>
       </c>
@@ -17484,16 +17484,16 @@
         </is>
       </c>
       <c r="U150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V150" t="n">
         <v>4</v>
       </c>
       <c r="W150" t="n">
+        <v>4</v>
+      </c>
+      <c r="X150" t="n">
         <v>9</v>
-      </c>
-      <c r="X150" t="n">
-        <v>1</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
@@ -17604,14 +17604,14 @@
           <t>2024-12-04</t>
         </is>
       </c>
-      <c r="U151" t="n">
-        <v>1</v>
-      </c>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="n">
-        <v>1</v>
-      </c>
-      <c r="X151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="n">
+        <v>1</v>
+      </c>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="n">
+        <v>1</v>
+      </c>
       <c r="Y151" t="n">
         <v>0</v>
       </c>
@@ -17721,15 +17721,15 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="n">
+      <c r="U152" t="n">
+        <v>1</v>
+      </c>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="n">
         <v>3</v>
       </c>
-      <c r="W152" t="n">
+      <c r="X152" t="n">
         <v>4</v>
-      </c>
-      <c r="X152" t="n">
-        <v>1</v>
       </c>
       <c r="Y152" t="n">
         <v>0</v>
@@ -17840,16 +17840,16 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="U153" t="n">
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="n">
         <v>6</v>
       </c>
-      <c r="V153" t="n">
+      <c r="W153" t="n">
         <v>2</v>
       </c>
-      <c r="W153" t="n">
+      <c r="X153" t="n">
         <v>8</v>
       </c>
-      <c r="X153" t="inlineStr"/>
       <c r="Y153" t="n">
         <v>0</v>
       </c>
@@ -17959,16 +17959,16 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="U154" t="n">
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="n">
         <v>4</v>
       </c>
-      <c r="V154" t="n">
+      <c r="W154" t="n">
         <v>2</v>
       </c>
-      <c r="W154" t="n">
+      <c r="X154" t="n">
         <v>6</v>
       </c>
-      <c r="X154" t="inlineStr"/>
       <c r="Y154" t="n">
         <v>0</v>
       </c>
@@ -18078,16 +18078,16 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="U155" t="n">
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="n">
         <v>5</v>
       </c>
-      <c r="V155" t="n">
+      <c r="W155" t="n">
         <v>9</v>
       </c>
-      <c r="W155" t="n">
+      <c r="X155" t="n">
         <v>14</v>
       </c>
-      <c r="X155" t="inlineStr"/>
       <c r="Y155" t="n">
         <v>0</v>
       </c>
@@ -18197,16 +18197,16 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="U156" t="n">
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="n">
         <v>5</v>
       </c>
-      <c r="V156" t="n">
+      <c r="W156" t="n">
         <v>7</v>
       </c>
-      <c r="W156" t="n">
+      <c r="X156" t="n">
         <v>12</v>
       </c>
-      <c r="X156" t="inlineStr"/>
       <c r="Y156" t="n">
         <v>0</v>
       </c>
@@ -18317,13 +18317,13 @@
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
-      <c r="V157" t="n">
-        <v>2</v>
-      </c>
+      <c r="V157" t="inlineStr"/>
       <c r="W157" t="n">
         <v>2</v>
       </c>
-      <c r="X157" t="inlineStr"/>
+      <c r="X157" t="n">
+        <v>2</v>
+      </c>
       <c r="Y157" t="n">
         <v>0</v>
       </c>
@@ -18434,13 +18434,13 @@
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
-      <c r="V158" t="n">
-        <v>2</v>
-      </c>
+      <c r="V158" t="inlineStr"/>
       <c r="W158" t="n">
         <v>2</v>
       </c>
-      <c r="X158" t="inlineStr"/>
+      <c r="X158" t="n">
+        <v>2</v>
+      </c>
       <c r="Y158" t="n">
         <v>0</v>
       </c>
@@ -18557,10 +18557,10 @@
         <v>1</v>
       </c>
       <c r="W159" t="n">
+        <v>1</v>
+      </c>
+      <c r="X159" t="n">
         <v>3</v>
-      </c>
-      <c r="X159" t="n">
-        <v>1</v>
       </c>
       <c r="Y159" t="n">
         <v>0</v>
@@ -18668,13 +18668,13 @@
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
-      <c r="V160" t="n">
-        <v>4</v>
-      </c>
+      <c r="V160" t="inlineStr"/>
       <c r="W160" t="n">
         <v>4</v>
       </c>
-      <c r="X160" t="inlineStr"/>
+      <c r="X160" t="n">
+        <v>4</v>
+      </c>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
       <c r="AA160" t="inlineStr"/>
@@ -18774,16 +18774,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U161" t="n">
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="n">
         <v>11</v>
       </c>
-      <c r="V161" t="n">
-        <v>1</v>
-      </c>
       <c r="W161" t="n">
+        <v>1</v>
+      </c>
+      <c r="X161" t="n">
         <v>12</v>
       </c>
-      <c r="X161" t="inlineStr"/>
       <c r="Y161" t="n">
         <v>0</v>
       </c>
@@ -18897,13 +18897,13 @@
         <v>1</v>
       </c>
       <c r="V162" t="n">
+        <v>1</v>
+      </c>
+      <c r="W162" t="n">
         <v>3</v>
       </c>
-      <c r="W162" t="n">
+      <c r="X162" t="n">
         <v>5</v>
-      </c>
-      <c r="X162" t="n">
-        <v>1</v>
       </c>
       <c r="Y162" t="n">
         <v>0</v>
@@ -19015,16 +19015,16 @@
         </is>
       </c>
       <c r="U163" t="n">
+        <v>1</v>
+      </c>
+      <c r="V163" t="n">
         <v>5</v>
       </c>
-      <c r="V163" t="n">
-        <v>1</v>
-      </c>
       <c r="W163" t="n">
+        <v>1</v>
+      </c>
+      <c r="X163" t="n">
         <v>7</v>
-      </c>
-      <c r="X163" t="n">
-        <v>1</v>
       </c>
       <c r="Y163" t="n">
         <v>0</v>
@@ -19136,13 +19136,13 @@
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
-      <c r="V164" t="n">
-        <v>3</v>
-      </c>
+      <c r="V164" t="inlineStr"/>
       <c r="W164" t="n">
         <v>3</v>
       </c>
-      <c r="X164" t="inlineStr"/>
+      <c r="X164" t="n">
+        <v>3</v>
+      </c>
       <c r="Y164" t="n">
         <v>1</v>
       </c>
@@ -19253,13 +19253,13 @@
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
-      <c r="V165" t="n">
-        <v>2</v>
-      </c>
+      <c r="V165" t="inlineStr"/>
       <c r="W165" t="n">
         <v>2</v>
       </c>
-      <c r="X165" t="inlineStr"/>
+      <c r="X165" t="n">
+        <v>2</v>
+      </c>
       <c r="Y165" t="n">
         <v>0</v>
       </c>
@@ -19369,16 +19369,16 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="U166" t="n">
-        <v>1</v>
-      </c>
+      <c r="U166" t="inlineStr"/>
       <c r="V166" t="n">
+        <v>1</v>
+      </c>
+      <c r="W166" t="n">
         <v>3</v>
       </c>
-      <c r="W166" t="n">
+      <c r="X166" t="n">
         <v>4</v>
       </c>
-      <c r="X166" t="inlineStr"/>
       <c r="Y166" t="n">
         <v>0</v>
       </c>
@@ -19488,16 +19488,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U167" t="n">
-        <v>1</v>
-      </c>
+      <c r="U167" t="inlineStr"/>
       <c r="V167" t="n">
+        <v>1</v>
+      </c>
+      <c r="W167" t="n">
         <v>2</v>
       </c>
-      <c r="W167" t="n">
+      <c r="X167" t="n">
         <v>3</v>
       </c>
-      <c r="X167" t="inlineStr"/>
       <c r="Y167" t="n">
         <v>0</v>
       </c>
@@ -19607,16 +19607,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U168" t="n">
-        <v>1</v>
-      </c>
+      <c r="U168" t="inlineStr"/>
       <c r="V168" t="n">
         <v>1</v>
       </c>
       <c r="W168" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" t="n">
         <v>2</v>
       </c>
-      <c r="X168" t="inlineStr"/>
       <c r="Y168" t="n">
         <v>0</v>
       </c>
@@ -19727,13 +19727,13 @@
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
-      <c r="V169" t="n">
-        <v>2</v>
-      </c>
+      <c r="V169" t="inlineStr"/>
       <c r="W169" t="n">
         <v>2</v>
       </c>
-      <c r="X169" t="inlineStr"/>
+      <c r="X169" t="n">
+        <v>2</v>
+      </c>
       <c r="Y169" t="n">
         <v>0</v>
       </c>
@@ -19843,14 +19843,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U170" t="n">
-        <v>1</v>
-      </c>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="n">
-        <v>1</v>
-      </c>
-      <c r="X170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="n">
+        <v>1</v>
+      </c>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="n">
+        <v>1</v>
+      </c>
       <c r="Y170" t="n">
         <v>0</v>
       </c>
@@ -19960,16 +19960,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U171" t="n">
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="n">
         <v>2</v>
       </c>
-      <c r="V171" t="n">
-        <v>1</v>
-      </c>
       <c r="W171" t="n">
+        <v>1</v>
+      </c>
+      <c r="X171" t="n">
         <v>3</v>
       </c>
-      <c r="X171" t="inlineStr"/>
       <c r="Y171" t="n">
         <v>0</v>
       </c>
@@ -20079,16 +20079,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U172" t="n">
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="n">
         <v>2</v>
       </c>
-      <c r="V172" t="n">
-        <v>1</v>
-      </c>
       <c r="W172" t="n">
+        <v>1</v>
+      </c>
+      <c r="X172" t="n">
         <v>3</v>
       </c>
-      <c r="X172" t="inlineStr"/>
       <c r="Y172" t="n">
         <v>0</v>
       </c>
@@ -20198,16 +20198,16 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U173" t="n">
-        <v>1</v>
-      </c>
+      <c r="U173" t="inlineStr"/>
       <c r="V173" t="n">
+        <v>1</v>
+      </c>
+      <c r="W173" t="n">
         <v>2</v>
       </c>
-      <c r="W173" t="n">
+      <c r="X173" t="n">
         <v>3</v>
       </c>
-      <c r="X173" t="inlineStr"/>
       <c r="Y173" t="n">
         <v>0</v>
       </c>
@@ -20317,16 +20317,16 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="U174" t="n">
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="n">
         <v>7</v>
       </c>
-      <c r="V174" t="n">
-        <v>1</v>
-      </c>
       <c r="W174" t="n">
+        <v>1</v>
+      </c>
+      <c r="X174" t="n">
         <v>8</v>
       </c>
-      <c r="X174" t="inlineStr"/>
       <c r="Y174" t="n">
         <v>2</v>
       </c>
@@ -20436,16 +20436,16 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U175" t="n">
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="n">
         <v>2</v>
       </c>
-      <c r="V175" t="n">
-        <v>1</v>
-      </c>
       <c r="W175" t="n">
+        <v>1</v>
+      </c>
+      <c r="X175" t="n">
         <v>3</v>
       </c>
-      <c r="X175" t="inlineStr"/>
       <c r="Y175" t="n">
         <v>0</v>
       </c>
@@ -20555,16 +20555,16 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="U176" t="n">
-        <v>2</v>
-      </c>
+      <c r="U176" t="inlineStr"/>
       <c r="V176" t="n">
         <v>2</v>
       </c>
       <c r="W176" t="n">
+        <v>2</v>
+      </c>
+      <c r="X176" t="n">
         <v>4</v>
       </c>
-      <c r="X176" t="inlineStr"/>
       <c r="Y176" t="n">
         <v>0</v>
       </c>
@@ -20675,16 +20675,16 @@
         </is>
       </c>
       <c r="U177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" t="n">
         <v>3</v>
       </c>
-      <c r="V177" t="n">
+      <c r="W177" t="n">
         <v>2</v>
       </c>
-      <c r="W177" t="n">
+      <c r="X177" t="n">
         <v>6</v>
-      </c>
-      <c r="X177" t="n">
-        <v>1</v>
       </c>
       <c r="Y177" t="n">
         <v>0</v>
@@ -20796,13 +20796,13 @@
         </is>
       </c>
       <c r="U178" t="inlineStr"/>
-      <c r="V178" t="n">
-        <v>2</v>
-      </c>
+      <c r="V178" t="inlineStr"/>
       <c r="W178" t="n">
         <v>2</v>
       </c>
-      <c r="X178" t="inlineStr"/>
+      <c r="X178" t="n">
+        <v>2</v>
+      </c>
       <c r="Y178" t="n">
         <v>0</v>
       </c>
@@ -20913,16 +20913,16 @@
         </is>
       </c>
       <c r="U179" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" t="n">
         <v>3</v>
       </c>
-      <c r="V179" t="n">
-        <v>1</v>
-      </c>
       <c r="W179" t="n">
+        <v>1</v>
+      </c>
+      <c r="X179" t="n">
         <v>5</v>
-      </c>
-      <c r="X179" t="n">
-        <v>1</v>
       </c>
       <c r="Y179" t="n">
         <v>0</v>
@@ -21036,12 +21036,12 @@
       <c r="U180" t="n">
         <v>1</v>
       </c>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="n">
+      <c r="V180" t="n">
+        <v>1</v>
+      </c>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="n">
         <v>2</v>
-      </c>
-      <c r="X180" t="n">
-        <v>1</v>
       </c>
       <c r="Y180" t="n">
         <v>0</v>
@@ -21152,14 +21152,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U181" t="n">
-        <v>1</v>
-      </c>
-      <c r="V181" t="inlineStr"/>
-      <c r="W181" t="n">
-        <v>1</v>
-      </c>
-      <c r="X181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="n">
+        <v>1</v>
+      </c>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="n">
+        <v>1</v>
+      </c>
       <c r="Y181" t="n">
         <v>0</v>
       </c>
@@ -21269,14 +21269,14 @@
           <t>2024-06-27</t>
         </is>
       </c>
-      <c r="U182" t="n">
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="n">
         <v>2</v>
       </c>
-      <c r="V182" t="inlineStr"/>
-      <c r="W182" t="n">
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="n">
         <v>2</v>
       </c>
-      <c r="X182" t="inlineStr"/>
       <c r="Y182" t="n">
         <v>1</v>
       </c>
@@ -21500,13 +21500,13 @@
         </is>
       </c>
       <c r="U184" t="inlineStr"/>
-      <c r="V184" t="n">
-        <v>2</v>
-      </c>
+      <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
         <v>2</v>
       </c>
-      <c r="X184" t="inlineStr"/>
+      <c r="X184" t="n">
+        <v>2</v>
+      </c>
       <c r="Y184" t="n">
         <v>0</v>
       </c>
@@ -21729,14 +21729,14 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="U186" t="n">
-        <v>1</v>
-      </c>
-      <c r="V186" t="inlineStr"/>
-      <c r="W186" t="n">
-        <v>1</v>
-      </c>
-      <c r="X186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="n">
+        <v>1</v>
+      </c>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="n">
+        <v>1</v>
+      </c>
       <c r="Y186" t="n">
         <v>0</v>
       </c>
@@ -21846,16 +21846,16 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="U187" t="n">
-        <v>1</v>
-      </c>
+      <c r="U187" t="inlineStr"/>
       <c r="V187" t="n">
         <v>1</v>
       </c>
       <c r="W187" t="n">
+        <v>1</v>
+      </c>
+      <c r="X187" t="n">
         <v>2</v>
       </c>
-      <c r="X187" t="inlineStr"/>
       <c r="Y187" t="n">
         <v>0</v>
       </c>
@@ -21966,13 +21966,13 @@
         </is>
       </c>
       <c r="U188" t="inlineStr"/>
-      <c r="V188" t="n">
-        <v>1</v>
-      </c>
+      <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
         <v>1</v>
       </c>
-      <c r="X188" t="inlineStr"/>
+      <c r="X188" t="n">
+        <v>1</v>
+      </c>
       <c r="Y188" t="n">
         <v>0</v>
       </c>
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="U189" t="inlineStr"/>
-      <c r="V189" t="n">
-        <v>1</v>
-      </c>
+      <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
         <v>1</v>
       </c>
-      <c r="X189" t="inlineStr"/>
+      <c r="X189" t="n">
+        <v>1</v>
+      </c>
       <c r="Y189" t="n">
         <v>0</v>
       </c>
@@ -22200,11 +22200,9 @@
         </is>
       </c>
       <c r="U190" t="inlineStr"/>
-      <c r="V190" t="n">
-        <v>1</v>
-      </c>
+      <c r="V190" t="inlineStr"/>
       <c r="W190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X190" t="n">
         <v>1</v>
@@ -22318,14 +22316,14 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="U191" t="n">
-        <v>1</v>
-      </c>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="n">
-        <v>1</v>
-      </c>
-      <c r="X191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="n">
+        <v>1</v>
+      </c>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="n">
+        <v>1</v>
+      </c>
       <c r="Y191" t="n">
         <v>0</v>
       </c>
@@ -22435,14 +22433,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U192" t="n">
-        <v>1</v>
-      </c>
-      <c r="V192" t="inlineStr"/>
-      <c r="W192" t="n">
-        <v>1</v>
-      </c>
-      <c r="X192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="n">
+        <v>1</v>
+      </c>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="n">
+        <v>1</v>
+      </c>
       <c r="Y192" t="n">
         <v>0</v>
       </c>
@@ -22555,12 +22553,12 @@
       <c r="U193" t="n">
         <v>1</v>
       </c>
-      <c r="V193" t="inlineStr"/>
-      <c r="W193" t="n">
+      <c r="V193" t="n">
+        <v>1</v>
+      </c>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="n">
         <v>2</v>
-      </c>
-      <c r="X193" t="n">
-        <v>1</v>
       </c>
       <c r="Y193" t="n">
         <v>0</v>
@@ -22671,16 +22669,16 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="U194" t="n">
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="n">
         <v>5</v>
       </c>
-      <c r="V194" t="n">
+      <c r="W194" t="n">
         <v>3</v>
       </c>
-      <c r="W194" t="n">
+      <c r="X194" t="n">
         <v>8</v>
       </c>
-      <c r="X194" t="inlineStr"/>
       <c r="Y194" t="n">
         <v>1</v>
       </c>
@@ -22790,16 +22788,16 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="U195" t="n">
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="n">
         <v>3</v>
       </c>
-      <c r="V195" t="n">
+      <c r="W195" t="n">
         <v>8</v>
       </c>
-      <c r="W195" t="n">
+      <c r="X195" t="n">
         <v>11</v>
       </c>
-      <c r="X195" t="inlineStr"/>
       <c r="Y195" t="n">
         <v>1</v>
       </c>
@@ -22909,14 +22907,14 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="U196" t="n">
-        <v>1</v>
-      </c>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="n">
-        <v>1</v>
-      </c>
-      <c r="X196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="n">
+        <v>1</v>
+      </c>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="n">
+        <v>1</v>
+      </c>
       <c r="Y196" t="n">
         <v>0</v>
       </c>
@@ -23026,16 +23024,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U197" t="n">
-        <v>1</v>
-      </c>
+      <c r="U197" t="inlineStr"/>
       <c r="V197" t="n">
+        <v>1</v>
+      </c>
+      <c r="W197" t="n">
         <v>2</v>
       </c>
-      <c r="W197" t="n">
+      <c r="X197" t="n">
         <v>3</v>
       </c>
-      <c r="X197" t="inlineStr"/>
       <c r="Y197" t="n">
         <v>0</v>
       </c>
@@ -23146,13 +23144,13 @@
         </is>
       </c>
       <c r="U198" t="inlineStr"/>
-      <c r="V198" t="n">
-        <v>3</v>
-      </c>
+      <c r="V198" t="inlineStr"/>
       <c r="W198" t="n">
         <v>3</v>
       </c>
-      <c r="X198" t="inlineStr"/>
+      <c r="X198" t="n">
+        <v>3</v>
+      </c>
       <c r="Y198" t="n">
         <v>0</v>
       </c>
@@ -23263,13 +23261,13 @@
         </is>
       </c>
       <c r="U199" t="inlineStr"/>
-      <c r="V199" t="n">
-        <v>2</v>
-      </c>
+      <c r="V199" t="inlineStr"/>
       <c r="W199" t="n">
         <v>2</v>
       </c>
-      <c r="X199" t="inlineStr"/>
+      <c r="X199" t="n">
+        <v>2</v>
+      </c>
       <c r="Y199" t="n">
         <v>0</v>
       </c>
@@ -23379,16 +23377,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U200" t="n">
-        <v>1</v>
-      </c>
+      <c r="U200" t="inlineStr"/>
       <c r="V200" t="n">
+        <v>1</v>
+      </c>
+      <c r="W200" t="n">
         <v>4</v>
       </c>
-      <c r="W200" t="n">
+      <c r="X200" t="n">
         <v>5</v>
       </c>
-      <c r="X200" t="inlineStr"/>
       <c r="Y200" t="n">
         <v>0</v>
       </c>
@@ -23499,13 +23497,13 @@
         </is>
       </c>
       <c r="U201" t="inlineStr"/>
-      <c r="V201" t="n">
-        <v>3</v>
-      </c>
+      <c r="V201" t="inlineStr"/>
       <c r="W201" t="n">
         <v>3</v>
       </c>
-      <c r="X201" t="inlineStr"/>
+      <c r="X201" t="n">
+        <v>3</v>
+      </c>
       <c r="Y201" t="n">
         <v>0</v>
       </c>
@@ -23728,14 +23726,14 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="U203" t="n">
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="n">
         <v>2</v>
       </c>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="n">
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="n">
         <v>2</v>
       </c>
-      <c r="X203" t="inlineStr"/>
       <c r="Y203" t="n">
         <v>0</v>
       </c>
@@ -23846,16 +23844,16 @@
         </is>
       </c>
       <c r="U204" t="n">
+        <v>1</v>
+      </c>
+      <c r="V204" t="n">
         <v>4</v>
       </c>
-      <c r="V204" t="n">
-        <v>1</v>
-      </c>
       <c r="W204" t="n">
+        <v>1</v>
+      </c>
+      <c r="X204" t="n">
         <v>6</v>
-      </c>
-      <c r="X204" t="n">
-        <v>1</v>
       </c>
       <c r="Y204" t="n">
         <v>0</v>
@@ -23967,16 +23965,16 @@
         </is>
       </c>
       <c r="U205" t="n">
+        <v>1</v>
+      </c>
+      <c r="V205" t="n">
         <v>2</v>
       </c>
-      <c r="V205" t="n">
-        <v>1</v>
-      </c>
       <c r="W205" t="n">
+        <v>1</v>
+      </c>
+      <c r="X205" t="n">
         <v>4</v>
-      </c>
-      <c r="X205" t="n">
-        <v>1</v>
       </c>
       <c r="Y205" t="n">
         <v>0</v>
@@ -24087,14 +24085,14 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="U206" t="n">
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="n">
         <v>2</v>
       </c>
-      <c r="V206" t="inlineStr"/>
-      <c r="W206" t="n">
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="n">
         <v>2</v>
       </c>
-      <c r="X206" t="inlineStr"/>
       <c r="Y206" t="n">
         <v>0</v>
       </c>
@@ -24204,14 +24202,14 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="U207" t="n">
-        <v>1</v>
-      </c>
-      <c r="V207" t="inlineStr"/>
-      <c r="W207" t="n">
-        <v>1</v>
-      </c>
-      <c r="X207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="n">
+        <v>1</v>
+      </c>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="n">
+        <v>1</v>
+      </c>
       <c r="Y207" t="n">
         <v>0</v>
       </c>
@@ -24321,16 +24319,16 @@
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="U208" t="n">
-        <v>3</v>
-      </c>
+      <c r="U208" t="inlineStr"/>
       <c r="V208" t="n">
         <v>3</v>
       </c>
       <c r="W208" t="n">
+        <v>3</v>
+      </c>
+      <c r="X208" t="n">
         <v>6</v>
       </c>
-      <c r="X208" t="inlineStr"/>
       <c r="Y208" t="n">
         <v>0</v>
       </c>
@@ -24669,12 +24667,12 @@
       <c r="U211" t="n">
         <v>1</v>
       </c>
-      <c r="V211" t="inlineStr"/>
-      <c r="W211" t="n">
+      <c r="V211" t="n">
+        <v>1</v>
+      </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="n">
         <v>2</v>
-      </c>
-      <c r="X211" t="n">
-        <v>1</v>
       </c>
       <c r="Y211" t="n">
         <v>0</v>
@@ -24781,13 +24779,13 @@
         <v>1</v>
       </c>
       <c r="V212" t="n">
+        <v>1</v>
+      </c>
+      <c r="W212" t="n">
         <v>2</v>
       </c>
-      <c r="W212" t="n">
+      <c r="X212" t="n">
         <v>4</v>
-      </c>
-      <c r="X212" t="n">
-        <v>1</v>
       </c>
       <c r="Y212" t="inlineStr"/>
       <c r="Z212" t="inlineStr"/>
@@ -24888,16 +24886,16 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="U213" t="n">
-        <v>1</v>
-      </c>
+      <c r="U213" t="inlineStr"/>
       <c r="V213" t="n">
+        <v>1</v>
+      </c>
+      <c r="W213" t="n">
         <v>2</v>
       </c>
-      <c r="W213" t="n">
+      <c r="X213" t="n">
         <v>3</v>
       </c>
-      <c r="X213" t="inlineStr"/>
       <c r="Y213" t="n">
         <v>0</v>
       </c>
@@ -25007,14 +25005,14 @@
           <t>2026-01-27</t>
         </is>
       </c>
-      <c r="U214" t="n">
-        <v>1</v>
-      </c>
-      <c r="V214" t="inlineStr"/>
-      <c r="W214" t="n">
-        <v>1</v>
-      </c>
-      <c r="X214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="n">
+        <v>1</v>
+      </c>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="n">
+        <v>1</v>
+      </c>
       <c r="Y214" t="n">
         <v>0</v>
       </c>
@@ -25124,16 +25122,16 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="U215" t="n">
-        <v>1</v>
-      </c>
+      <c r="U215" t="inlineStr"/>
       <c r="V215" t="n">
+        <v>1</v>
+      </c>
+      <c r="W215" t="n">
         <v>2</v>
       </c>
-      <c r="W215" t="n">
+      <c r="X215" t="n">
         <v>3</v>
       </c>
-      <c r="X215" t="inlineStr"/>
       <c r="Y215" t="n">
         <v>0</v>
       </c>
@@ -25243,14 +25241,14 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="U216" t="n">
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="n">
         <v>2</v>
       </c>
-      <c r="V216" t="inlineStr"/>
-      <c r="W216" t="n">
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="n">
         <v>2</v>
       </c>
-      <c r="X216" t="inlineStr"/>
       <c r="Y216" t="n">
         <v>0</v>
       </c>
@@ -25360,16 +25358,16 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="U217" t="n">
-        <v>1</v>
-      </c>
+      <c r="U217" t="inlineStr"/>
       <c r="V217" t="n">
+        <v>1</v>
+      </c>
+      <c r="W217" t="n">
         <v>2</v>
       </c>
-      <c r="W217" t="n">
+      <c r="X217" t="n">
         <v>3</v>
       </c>
-      <c r="X217" t="inlineStr"/>
       <c r="Y217" t="n">
         <v>0</v>
       </c>
@@ -25483,13 +25481,13 @@
         <v>1</v>
       </c>
       <c r="V218" t="n">
+        <v>1</v>
+      </c>
+      <c r="W218" t="n">
         <v>3</v>
       </c>
-      <c r="W218" t="n">
+      <c r="X218" t="n">
         <v>5</v>
-      </c>
-      <c r="X218" t="n">
-        <v>1</v>
       </c>
       <c r="Y218" t="n">
         <v>0</v>
@@ -25601,16 +25599,16 @@
         </is>
       </c>
       <c r="U219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V219" t="n">
+        <v>1</v>
+      </c>
+      <c r="W219" t="n">
         <v>3</v>
       </c>
-      <c r="W219" t="n">
+      <c r="X219" t="n">
         <v>6</v>
-      </c>
-      <c r="X219" t="n">
-        <v>2</v>
       </c>
       <c r="Y219" t="n">
         <v>0</v>
@@ -25721,16 +25719,16 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="U220" t="n">
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="n">
         <v>2</v>
       </c>
-      <c r="V220" t="n">
+      <c r="W220" t="n">
         <v>4</v>
       </c>
-      <c r="W220" t="n">
+      <c r="X220" t="n">
         <v>6</v>
       </c>
-      <c r="X220" t="inlineStr"/>
       <c r="Y220" t="n">
         <v>0</v>
       </c>
@@ -25841,14 +25839,14 @@
         </is>
       </c>
       <c r="U221" t="n">
-        <v>1</v>
-      </c>
-      <c r="V221" t="inlineStr"/>
-      <c r="W221" t="n">
+        <v>2</v>
+      </c>
+      <c r="V221" t="n">
+        <v>1</v>
+      </c>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="n">
         <v>3</v>
-      </c>
-      <c r="X221" t="n">
-        <v>2</v>
       </c>
       <c r="Y221" t="n">
         <v>0</v>
@@ -25959,16 +25957,16 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="U222" t="n">
-        <v>1</v>
-      </c>
+      <c r="U222" t="inlineStr"/>
       <c r="V222" t="n">
+        <v>1</v>
+      </c>
+      <c r="W222" t="n">
         <v>2</v>
       </c>
-      <c r="W222" t="n">
+      <c r="X222" t="n">
         <v>3</v>
       </c>
-      <c r="X222" t="inlineStr"/>
       <c r="Y222" t="n">
         <v>0</v>
       </c>
@@ -26078,16 +26076,16 @@
           <t>2025-05-08</t>
         </is>
       </c>
-      <c r="U223" t="n">
-        <v>1</v>
-      </c>
+      <c r="U223" t="inlineStr"/>
       <c r="V223" t="n">
+        <v>1</v>
+      </c>
+      <c r="W223" t="n">
         <v>2</v>
       </c>
-      <c r="W223" t="n">
+      <c r="X223" t="n">
         <v>3</v>
       </c>
-      <c r="X223" t="inlineStr"/>
       <c r="Y223" t="n">
         <v>0</v>
       </c>
@@ -26197,16 +26195,16 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="U224" t="n">
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="n">
         <v>2</v>
       </c>
-      <c r="V224" t="n">
-        <v>1</v>
-      </c>
       <c r="W224" t="n">
+        <v>1</v>
+      </c>
+      <c r="X224" t="n">
         <v>3</v>
       </c>
-      <c r="X224" t="inlineStr"/>
       <c r="Y224" t="n">
         <v>0</v>
       </c>
@@ -26317,14 +26315,14 @@
         </is>
       </c>
       <c r="U225" t="n">
-        <v>1</v>
-      </c>
-      <c r="V225" t="inlineStr"/>
-      <c r="W225" t="n">
+        <v>2</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1</v>
+      </c>
+      <c r="W225" t="inlineStr"/>
+      <c r="X225" t="n">
         <v>3</v>
-      </c>
-      <c r="X225" t="n">
-        <v>2</v>
       </c>
       <c r="Y225" t="n">
         <v>0</v>
@@ -26438,12 +26436,12 @@
       <c r="U226" t="n">
         <v>1</v>
       </c>
-      <c r="V226" t="inlineStr"/>
-      <c r="W226" t="n">
+      <c r="V226" t="n">
+        <v>1</v>
+      </c>
+      <c r="W226" t="inlineStr"/>
+      <c r="X226" t="n">
         <v>2</v>
-      </c>
-      <c r="X226" t="n">
-        <v>1</v>
       </c>
       <c r="Y226" t="n">
         <v>0</v>
@@ -26555,14 +26553,14 @@
         </is>
       </c>
       <c r="U227" t="n">
+        <v>1</v>
+      </c>
+      <c r="V227" t="n">
         <v>2</v>
       </c>
-      <c r="V227" t="inlineStr"/>
-      <c r="W227" t="n">
+      <c r="W227" t="inlineStr"/>
+      <c r="X227" t="n">
         <v>3</v>
-      </c>
-      <c r="X227" t="n">
-        <v>1</v>
       </c>
       <c r="Y227" t="n">
         <v>0</v>
@@ -26676,12 +26674,12 @@
       <c r="U228" t="n">
         <v>1</v>
       </c>
-      <c r="V228" t="inlineStr"/>
-      <c r="W228" t="n">
+      <c r="V228" t="n">
+        <v>1</v>
+      </c>
+      <c r="W228" t="inlineStr"/>
+      <c r="X228" t="n">
         <v>2</v>
-      </c>
-      <c r="X228" t="n">
-        <v>1</v>
       </c>
       <c r="Y228" t="n">
         <v>2</v>
@@ -26792,14 +26790,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U229" t="n">
-        <v>1</v>
-      </c>
-      <c r="V229" t="inlineStr"/>
-      <c r="W229" t="n">
-        <v>1</v>
-      </c>
-      <c r="X229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="n">
+        <v>1</v>
+      </c>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="n">
+        <v>1</v>
+      </c>
       <c r="Y229" t="n">
         <v>2</v>
       </c>
@@ -26909,14 +26907,14 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="U230" t="n">
-        <v>1</v>
-      </c>
-      <c r="V230" t="inlineStr"/>
-      <c r="W230" t="n">
-        <v>1</v>
-      </c>
-      <c r="X230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="n">
+        <v>1</v>
+      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="n">
+        <v>1</v>
+      </c>
       <c r="Y230" t="n">
         <v>0</v>
       </c>
@@ -27026,14 +27024,14 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="U231" t="n">
-        <v>1</v>
-      </c>
-      <c r="V231" t="inlineStr"/>
-      <c r="W231" t="n">
-        <v>1</v>
-      </c>
-      <c r="X231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="n">
+        <v>1</v>
+      </c>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="n">
+        <v>1</v>
+      </c>
       <c r="Y231" t="n">
         <v>0</v>
       </c>
@@ -27143,14 +27141,14 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="U232" t="n">
-        <v>1</v>
-      </c>
-      <c r="V232" t="inlineStr"/>
-      <c r="W232" t="n">
-        <v>1</v>
-      </c>
-      <c r="X232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="n">
+        <v>1</v>
+      </c>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="n">
+        <v>1</v>
+      </c>
       <c r="Y232" t="n">
         <v>0</v>
       </c>
@@ -27267,10 +27265,10 @@
         <v>1</v>
       </c>
       <c r="W233" t="n">
+        <v>1</v>
+      </c>
+      <c r="X233" t="n">
         <v>3</v>
-      </c>
-      <c r="X233" t="n">
-        <v>1</v>
       </c>
       <c r="Y233" t="n">
         <v>0</v>
@@ -27381,14 +27379,14 @@
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="U234" t="n">
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="n">
         <v>3</v>
       </c>
-      <c r="V234" t="inlineStr"/>
-      <c r="W234" t="n">
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="n">
         <v>3</v>
       </c>
-      <c r="X234" t="inlineStr"/>
       <c r="Y234" t="n">
         <v>0</v>
       </c>
@@ -27498,16 +27496,16 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="U235" t="n">
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="n">
         <v>4</v>
       </c>
-      <c r="V235" t="n">
+      <c r="W235" t="n">
         <v>3</v>
       </c>
-      <c r="W235" t="n">
+      <c r="X235" t="n">
         <v>7</v>
       </c>
-      <c r="X235" t="inlineStr"/>
       <c r="Y235" t="n">
         <v>0</v>
       </c>
@@ -27617,16 +27615,16 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="U236" t="n">
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="n">
         <v>2</v>
       </c>
-      <c r="V236" t="n">
-        <v>1</v>
-      </c>
       <c r="W236" t="n">
+        <v>1</v>
+      </c>
+      <c r="X236" t="n">
         <v>3</v>
       </c>
-      <c r="X236" t="inlineStr"/>
       <c r="Y236" t="n">
         <v>0</v>
       </c>
@@ -27736,14 +27734,14 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="U237" t="n">
-        <v>1</v>
-      </c>
-      <c r="V237" t="inlineStr"/>
-      <c r="W237" t="n">
-        <v>1</v>
-      </c>
-      <c r="X237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="n">
+        <v>1</v>
+      </c>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="n">
+        <v>1</v>
+      </c>
       <c r="Y237" t="n">
         <v>0</v>
       </c>
@@ -27853,14 +27851,14 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="U238" t="n">
-        <v>1</v>
-      </c>
-      <c r="V238" t="inlineStr"/>
-      <c r="W238" t="n">
-        <v>1</v>
-      </c>
-      <c r="X238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="n">
+        <v>1</v>
+      </c>
+      <c r="W238" t="inlineStr"/>
+      <c r="X238" t="n">
+        <v>1</v>
+      </c>
       <c r="Y238" t="n">
         <v>0</v>
       </c>
@@ -27974,13 +27972,13 @@
         <v>1</v>
       </c>
       <c r="V239" t="n">
+        <v>1</v>
+      </c>
+      <c r="W239" t="n">
         <v>2</v>
       </c>
-      <c r="W239" t="n">
+      <c r="X239" t="n">
         <v>4</v>
-      </c>
-      <c r="X239" t="n">
-        <v>1</v>
       </c>
       <c r="Y239" t="n">
         <v>1</v>
@@ -28098,10 +28096,10 @@
         <v>1</v>
       </c>
       <c r="W240" t="n">
+        <v>1</v>
+      </c>
+      <c r="X240" t="n">
         <v>3</v>
-      </c>
-      <c r="X240" t="n">
-        <v>1</v>
       </c>
       <c r="Y240" t="n">
         <v>1</v>
@@ -28212,16 +28210,16 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="U241" t="n">
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="n">
         <v>2</v>
       </c>
-      <c r="V241" t="n">
-        <v>1</v>
-      </c>
       <c r="W241" t="n">
+        <v>1</v>
+      </c>
+      <c r="X241" t="n">
         <v>3</v>
       </c>
-      <c r="X241" t="inlineStr"/>
       <c r="Y241" t="n">
         <v>1</v>
       </c>
@@ -28331,14 +28329,14 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="U242" t="n">
-        <v>1</v>
-      </c>
-      <c r="V242" t="inlineStr"/>
-      <c r="W242" t="n">
-        <v>1</v>
-      </c>
-      <c r="X242" t="inlineStr"/>
+      <c r="U242" t="inlineStr"/>
+      <c r="V242" t="n">
+        <v>1</v>
+      </c>
+      <c r="W242" t="inlineStr"/>
+      <c r="X242" t="n">
+        <v>1</v>
+      </c>
       <c r="Y242" t="n">
         <v>0</v>
       </c>
@@ -28448,16 +28446,16 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="U243" t="n">
-        <v>1</v>
-      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="n">
+        <v>1</v>
+      </c>
+      <c r="W243" t="n">
         <v>3</v>
       </c>
-      <c r="W243" t="n">
+      <c r="X243" t="n">
         <v>4</v>
       </c>
-      <c r="X243" t="inlineStr"/>
       <c r="Y243" t="n">
         <v>0</v>
       </c>
@@ -28567,16 +28565,16 @@
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="U244" t="n">
-        <v>1</v>
-      </c>
+      <c r="U244" t="inlineStr"/>
       <c r="V244" t="n">
+        <v>1</v>
+      </c>
+      <c r="W244" t="n">
         <v>2</v>
       </c>
-      <c r="W244" t="n">
+      <c r="X244" t="n">
         <v>3</v>
       </c>
-      <c r="X244" t="inlineStr"/>
       <c r="Y244" t="n">
         <v>0</v>
       </c>
@@ -28686,14 +28684,14 @@
           <t>2026-01-30</t>
         </is>
       </c>
-      <c r="U245" t="n">
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="n">
         <v>2</v>
       </c>
-      <c r="V245" t="inlineStr"/>
-      <c r="W245" t="n">
+      <c r="W245" t="inlineStr"/>
+      <c r="X245" t="n">
         <v>2</v>
       </c>
-      <c r="X245" t="inlineStr"/>
       <c r="Y245" t="n">
         <v>0</v>
       </c>
@@ -28803,16 +28801,16 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="U246" t="n">
-        <v>1</v>
-      </c>
+      <c r="U246" t="inlineStr"/>
       <c r="V246" t="n">
+        <v>1</v>
+      </c>
+      <c r="W246" t="n">
         <v>2</v>
       </c>
-      <c r="W246" t="n">
+      <c r="X246" t="n">
         <v>3</v>
       </c>
-      <c r="X246" t="inlineStr"/>
       <c r="Y246" t="n">
         <v>0</v>
       </c>
@@ -28915,16 +28913,16 @@
         </is>
       </c>
       <c r="U247" t="n">
+        <v>1</v>
+      </c>
+      <c r="V247" t="n">
         <v>2</v>
       </c>
-      <c r="V247" t="n">
+      <c r="W247" t="n">
         <v>3</v>
       </c>
-      <c r="W247" t="n">
+      <c r="X247" t="n">
         <v>6</v>
-      </c>
-      <c r="X247" t="n">
-        <v>1</v>
       </c>
       <c r="Y247" t="inlineStr"/>
       <c r="Z247" t="inlineStr"/>
@@ -29026,13 +29024,13 @@
         </is>
       </c>
       <c r="U248" t="inlineStr"/>
-      <c r="V248" t="n">
-        <v>1</v>
-      </c>
+      <c r="V248" t="inlineStr"/>
       <c r="W248" t="n">
         <v>1</v>
       </c>
-      <c r="X248" t="inlineStr"/>
+      <c r="X248" t="n">
+        <v>1</v>
+      </c>
       <c r="Y248" t="n">
         <v>0</v>
       </c>
@@ -29142,14 +29140,14 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="U249" t="n">
-        <v>1</v>
-      </c>
-      <c r="V249" t="inlineStr"/>
-      <c r="W249" t="n">
-        <v>1</v>
-      </c>
-      <c r="X249" t="inlineStr"/>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="n">
+        <v>1</v>
+      </c>
+      <c r="W249" t="inlineStr"/>
+      <c r="X249" t="n">
+        <v>1</v>
+      </c>
       <c r="Y249" t="n">
         <v>0</v>
       </c>
@@ -29262,12 +29260,12 @@
       <c r="U250" t="n">
         <v>1</v>
       </c>
-      <c r="V250" t="inlineStr"/>
-      <c r="W250" t="n">
+      <c r="V250" t="n">
+        <v>1</v>
+      </c>
+      <c r="W250" t="inlineStr"/>
+      <c r="X250" t="n">
         <v>2</v>
-      </c>
-      <c r="X250" t="n">
-        <v>1</v>
       </c>
       <c r="Y250" t="n">
         <v>1</v>
@@ -29289,12 +29287,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>1ea8fc1b-b913-41e5-b9ce-4f23be6fb992</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_c7466354-bacc-4781-acdc-543dd03d1eab</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -29304,7 +29302,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Nanwakolas LiDAR Surveys - Airborne Coastal Observatory</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -29314,7 +29312,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H251" t="b">
@@ -29350,12 +29348,12 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8, 49.26], [-124.5, 49.26], [-124.5, 50.83], [-126.8, 50.83], [-126.8, 49.26]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>[{'max': '1700.0', 'min': '0.0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
@@ -29365,7 +29363,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/e0r7-ge27</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -29378,17 +29376,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="U251" t="n">
-        <v>4</v>
-      </c>
-      <c r="V251" t="n">
-        <v>3</v>
-      </c>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr"/>
       <c r="W251" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y251" t="n">
         <v>0</v>
@@ -29410,12 +29404,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -29425,7 +29419,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -29443,12 +29437,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -29467,46 +29461,48 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/a0v4-x512</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U252" t="inlineStr"/>
       <c r="V252" t="n">
+        <v>1</v>
+      </c>
+      <c r="W252" t="n">
+        <v>1</v>
+      </c>
+      <c r="X252" t="n">
         <v>2</v>
       </c>
-      <c r="W252" t="n">
-        <v>2</v>
-      </c>
-      <c r="X252" t="inlineStr"/>
       <c r="Y252" t="n">
         <v>0</v>
       </c>
@@ -29527,12 +29523,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -29542,7 +29538,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -29560,7 +29556,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -29584,26 +29580,26 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -29613,19 +29609,17 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="U253" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr"/>
       <c r="V253" t="n">
         <v>1</v>
       </c>
-      <c r="W253" t="n">
-        <v>2</v>
-      </c>
-      <c r="X253" t="inlineStr"/>
+      <c r="W253" t="inlineStr"/>
+      <c r="X253" t="n">
+        <v>1</v>
+      </c>
       <c r="Y253" t="n">
         <v>0</v>
       </c>
@@ -29646,12 +29640,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -29661,7 +29655,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -29679,12 +29673,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -29707,42 +29701,42 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="U254" t="n">
-        <v>1</v>
-      </c>
-      <c r="V254" t="inlineStr"/>
-      <c r="W254" t="n">
-        <v>1</v>
-      </c>
-      <c r="X254" t="inlineStr"/>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="n">
+        <v>1</v>
+      </c>
+      <c r="W254" t="inlineStr"/>
+      <c r="X254" t="n">
+        <v>1</v>
+      </c>
       <c r="Y254" t="n">
         <v>0</v>
       </c>
@@ -29763,12 +29757,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -29778,7 +29772,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -29796,12 +29790,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -29820,45 +29814,41 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="U255" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
-      <c r="W255" t="n">
-        <v>1</v>
-      </c>
+      <c r="W255" t="inlineStr"/>
       <c r="X255" t="inlineStr"/>
       <c r="Y255" t="n">
         <v>0</v>
@@ -29880,12 +29870,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -29895,7 +29885,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -29913,7 +29903,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -29937,42 +29927,48 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>10.21966/65d8-k051</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr"/>
+      <c r="V256" t="n">
+        <v>1</v>
+      </c>
+      <c r="W256" t="n">
         <v>2</v>
       </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>10.21966/kace-2d24</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr"/>
-      <c r="V256" t="inlineStr"/>
-      <c r="W256" t="inlineStr"/>
-      <c r="X256" t="inlineStr"/>
+      <c r="X256" t="n">
+        <v>3</v>
+      </c>
       <c r="Y256" t="n">
         <v>0</v>
       </c>
@@ -29993,12 +29989,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30008,7 +30004,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -30026,12 +30022,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -30050,59 +30046,59 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U257" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr"/>
       <c r="V257" t="n">
+        <v>1</v>
+      </c>
+      <c r="W257" t="n">
         <v>2</v>
       </c>
-      <c r="W257" t="n">
+      <c r="X257" t="n">
         <v>3</v>
       </c>
-      <c r="X257" t="inlineStr"/>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
         </is>
       </c>
     </row>
@@ -30112,12 +30108,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -30127,7 +30123,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -30145,7 +30141,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -30173,55 +30169,55 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="U258" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr"/>
       <c r="V258" t="n">
+        <v>1</v>
+      </c>
+      <c r="W258" t="n">
         <v>2</v>
       </c>
-      <c r="W258" t="n">
+      <c r="X258" t="n">
         <v>3</v>
       </c>
-      <c r="X258" t="inlineStr"/>
       <c r="Y258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -30231,12 +30227,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -30246,7 +30242,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -30264,12 +30260,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -30288,48 +30284,48 @@
         </is>
       </c>
       <c r="N259" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>10.21966/3q5j-n957</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="n">
+        <v>1</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1</v>
+      </c>
+      <c r="X259" t="n">
         <v>2</v>
       </c>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
-        </is>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R259" t="inlineStr">
-        <is>
-          <t>10.21966/0xvh-1318</t>
-        </is>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="T259" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="U259" t="n">
-        <v>1</v>
-      </c>
-      <c r="V259" t="n">
-        <v>2</v>
-      </c>
-      <c r="W259" t="n">
-        <v>3</v>
-      </c>
-      <c r="X259" t="inlineStr"/>
       <c r="Y259" t="n">
         <v>0</v>
       </c>
@@ -30350,12 +30346,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -30365,7 +30361,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -30383,12 +30379,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -30403,7 +30399,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -30411,32 +30407,28 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>10.21966/w9n0-kn30</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U260" t="n">
@@ -30446,9 +30438,11 @@
         <v>1</v>
       </c>
       <c r="W260" t="n">
-        <v>2</v>
-      </c>
-      <c r="X260" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="X260" t="n">
+        <v>5</v>
+      </c>
       <c r="Y260" t="n">
         <v>0</v>
       </c>
@@ -30458,123 +30452,6 @@
         </is>
       </c>
       <c r="AA260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>259</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="H261" t="b">
-        <v>0</v>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Tula Foundation</t>
-        </is>
-      </c>
-      <c r="N261" t="n">
-        <v>1</v>
-      </c>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
-        </is>
-      </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
-        </is>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>10.21966/w9n0-kn30</t>
-        </is>
-      </c>
-      <c r="S261" t="inlineStr"/>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="U261" t="n">
-        <v>1</v>
-      </c>
-      <c r="V261" t="n">
-        <v>3</v>
-      </c>
-      <c r="W261" t="n">
-        <v>5</v>
-      </c>
-      <c r="X261" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y261" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA261" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
